--- a/src/main/resources/python/MultifacetedModeling/Results/OnTrain/KnowledgeKernel/MLR/0.xlsx
+++ b/src/main/resources/python/MultifacetedModeling/Results/OnTrain/KnowledgeKernel/MLR/0.xlsx
@@ -442,56 +442,56 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>1.083984375</t>
+          <t>1.298828125</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1.474609375</t>
+          <t>1.103515625</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>1.298828125</t>
+          <t>1.474609375</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>1.083984375</t>
+          <t>1.044921875</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0.673828125</t>
+          <t>1.11328125</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>1.376953125</t>
+          <t>1.474609375</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0.91796875</t>
+          <t>1.46484375</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>1.044921875</t>
+          <t>1.220703125</t>
         </is>
       </c>
     </row>
@@ -505,91 +505,91 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>1.474609375</t>
+          <t>0.78125</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0.908203125</t>
+          <t>1.455078125</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>1.50390625</t>
+          <t>1.171875</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>1.005859375</t>
+          <t>0.64453125</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0.791015625</t>
+          <t>1.484375</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>1.34765625</t>
+          <t>0.830078125</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>1.15234375</t>
+          <t>1.328125</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>1.357421875</t>
+          <t>0.908203125</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>1.23046875</t>
+          <t>0.869140625</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>1.259765625</t>
+          <t>1.044921875</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>1.474609375</t>
+          <t>1.298828125</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0.64453125</t>
+          <t>1.240234375</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>1.2109375</t>
+          <t>0.68359375</t>
         </is>
       </c>
     </row>
@@ -617,154 +617,154 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>1.266462844402132</t>
+          <t>1.3449816616314438</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1.28845608365266</t>
+          <t>1.3926220288289175</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>1.3223623274972243</t>
+          <t>1.4496197577710896</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>1.2939543934652922</t>
+          <t>1.001451127838361</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0.948156030463173</t>
+          <t>1.147756228034354</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>1.1473327984617712</t>
+          <t>1.4196443443344644</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>1.1473327984617712</t>
+          <t>1.4232484288040896</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>1.1473327984617712</t>
+          <t>1.2461821894875773</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>1.1473327984617712</t>
+          <t>0.9285333893514989</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>1.28845608365266</t>
+          <t>0.8502560835238944</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>1.1473327984617712</t>
+          <t>1.4048740916807483</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>1.1473327984617712</t>
+          <t>1.423344532225026</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>1.1473327984617712</t>
+          <t>0.6247046070708732</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>1.1473327984617712</t>
+          <t>1.4363455606685323</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>1.1473327984617712</t>
+          <t>0.4857281122015532</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>1.1473327984617712</t>
+          <t>1.1723375426938076</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>1.1473327984617712</t>
+          <t>0.5444552096055723</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>1.1473327984617712</t>
+          <t>0.9034058807684902</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>1.3150312477470483</t>
+          <t>1.10030928641671</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>1.3269442523410844</t>
+          <t>1.2468339507178325</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0.948156030463173</t>
+          <t>1.2070753091307453</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>1.3452719517165244</t>
+          <t>0.7236972439634913</t>
         </is>
       </c>
     </row>
@@ -802,17 +802,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0.1965600745020745</t>
+          <t>0.07671175258821224</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0.20225651881264803</t>
+          <t>0.15559261866495958</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.35004575125061177</t>
+          <t>0.6404605886482517</t>
         </is>
       </c>
     </row>
